--- a/Project_ETF/ETF_Investment_Portfolio/009819/ETF_Investment_Portfolio_20261019.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/009819/ETF_Investment_Portfolio_20261019.xlsx
@@ -1151,17 +1151,17 @@
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>CRDO US</t>
+          <t>AEE US</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>Credo科技集團控股有限公司</t>
+          <t>阿莫林公司</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>9,366</t>
+          <t>15,531</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
@@ -1173,17 +1173,17 @@
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>AEE US</t>
+          <t>CRDO US</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>阿莫林公司</t>
+          <t>Credo科技集團控股有限公司</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>15,531</t>
+          <t>9,366</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
